--- a/settings/data/StageProcess.xlsx
+++ b/settings/data/StageProcess.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectFiles\LOO\touhou_LOO-master\touhou_LOO-master\settings\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C1B2D7-E212-4383-BAED-1FC742B5A1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Stage1" sheetId="1" r:id="rId1"/>
@@ -27,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="34">
   <si>
     <t>string</t>
   </si>
@@ -52,6 +48,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">类型
 </t>
     </r>
@@ -60,7 +63,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -72,7 +74,6 @@
         <sz val="10"/>
         <color theme="4"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -90,7 +91,6 @@
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -102,7 +102,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -127,7 +126,29 @@
         <sz val="16"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">敌人属性强化
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生成敌人的伤害、血量在基础值的基础上乘算该数值。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -139,7 +160,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -148,14 +168,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">速度强化
 </t>
     </r>
@@ -164,7 +176,6 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -172,59 +183,8 @@
     </r>
   </si>
   <si>
-    <t>event_id</t>
-  </si>
-  <si>
-    <t>spawn_type</t>
-  </si>
-  <si>
-    <t>*id</t>
-  </si>
-  <si>
-    <t>start_time</t>
-  </si>
-  <si>
-    <t>end_time</t>
-  </si>
-  <si>
-    <t>tick_time</t>
-  </si>
-  <si>
-    <t>enemy_type</t>
-  </si>
-  <si>
-    <t>amount_parameter</t>
-  </si>
-  <si>
-    <t>enemy_attribute_boost</t>
-  </si>
-  <si>
-    <t>enemy_barrage_boost</t>
-  </si>
-  <si>
-    <t>speed_boost</t>
-  </si>
-  <si>
-    <t>zako</t>
-  </si>
-  <si>
-    <t>elite</t>
-  </si>
-  <si>
-    <t>enm_eltkedama</t>
-  </si>
-  <si>
-    <t>evt_boss</t>
-  </si>
-  <si>
-    <t>boss</t>
-  </si>
-  <si>
-    <t>keine</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">敌人属性强化
+      <t xml:space="preserve">碎片倍率
 </t>
     </r>
     <r>
@@ -232,20 +192,78 @@
         <sz val="10"/>
         <color theme="9"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>生成敌人的伤害、血量在基础值的基础上乘算该数值。</t>
+      <t>生成敌人掉落的碎片数在基础值的基础上乘算该数值。</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_id</t>
+  </si>
+  <si>
+    <t>spawn_type</t>
+  </si>
+  <si>
+    <t>*id</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t>end_time</t>
+  </si>
+  <si>
+    <t>tick_time</t>
+  </si>
+  <si>
+    <t>enemy_type</t>
+  </si>
+  <si>
+    <t>amount_parameter</t>
+  </si>
+  <si>
+    <t>enemy_attribute_boost</t>
+  </si>
+  <si>
+    <t>enemy_barrage_boost</t>
+  </si>
+  <si>
+    <t>speed_boost</t>
+  </si>
+  <si>
+    <t>piece_boost</t>
+  </si>
+  <si>
+    <t>zako</t>
+  </si>
+  <si>
+    <t>elite</t>
+  </si>
+  <si>
+    <t>enm_eltkedama</t>
+  </si>
+  <si>
+    <t>evt_boss</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>keine</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,7 +275,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -265,15 +282,157 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -281,27 +440,205 @@
       <sz val="10"/>
       <color theme="4"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -324,9 +661,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -347,24 +926,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Enemy"/>
@@ -676,29 +1299,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.08984375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.08984375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.0925925925926" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.09259259259259" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.8148148148148" style="2" customWidth="1"/>
     <col min="5" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.453125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.453125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.81640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.81640625" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="18.9074074074074" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.4537037037037" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.4537037037037" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.8148148148148" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.8148148148148" style="2" customWidth="1"/>
+    <col min="12" max="12" width="24.6666666666667" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -732,8 +1356,11 @@
       <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="151" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="164.4" spans="1:12">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -759,57 +1386,63 @@
         <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="2" t="str">
         <f>"evt_"&amp;B4&amp;"_"&amp;C4</f>
         <v>evt_zako_1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
@@ -839,14 +1472,17 @@
       <c r="K4" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="2" t="str">
         <f t="shared" ref="A5:A32" si="0">"evt_"&amp;B5&amp;"_"&amp;C5</f>
         <v>evt_zako_2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
@@ -876,14 +1512,17 @@
       <c r="K5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -913,14 +1552,17 @@
       <c r="K6" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -944,14 +1586,17 @@
       <c r="K7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2">
         <v>4</v>
@@ -981,14 +1626,17 @@
       <c r="K8" s="2">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2">
         <v>5</v>
@@ -1018,14 +1666,17 @@
       <c r="K9" s="2">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>6</v>
@@ -1055,14 +1706,17 @@
       <c r="K10" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
@@ -1071,7 +1725,7 @@
         <v>120</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -1085,14 +1739,17 @@
       <c r="K11" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_7</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2">
         <v>7</v>
@@ -1122,14 +1779,17 @@
       <c r="K12" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2">
         <v>8</v>
@@ -1159,14 +1819,17 @@
       <c r="K13" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
@@ -1190,14 +1853,17 @@
       <c r="K14" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2">
         <v>9</v>
@@ -1227,14 +1893,17 @@
       <c r="K15" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_10</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2">
         <v>10</v>
@@ -1264,14 +1933,17 @@
       <c r="K16" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
@@ -1295,14 +1967,17 @@
       <c r="K17" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2">
         <v>11</v>
@@ -1332,14 +2007,17 @@
       <c r="K18" s="2">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C19" s="2">
         <v>12</v>
@@ -1369,14 +2047,17 @@
       <c r="K19" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_5</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2">
         <v>5</v>
@@ -1385,7 +2066,7 @@
         <v>210</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2">
         <v>2</v>
@@ -1399,14 +2080,17 @@
       <c r="K20" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C21" s="2">
         <v>13</v>
@@ -1436,14 +2120,17 @@
       <c r="K21" s="2">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2">
         <v>14</v>
@@ -1473,14 +2160,17 @@
       <c r="K22" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C23" s="2">
         <v>6</v>
@@ -1504,14 +2194,17 @@
       <c r="K23" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C24" s="2">
         <v>7</v>
@@ -1520,7 +2213,7 @@
         <v>240</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -1534,14 +2227,17 @@
       <c r="K24" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C25" s="2">
         <v>8</v>
@@ -1565,14 +2261,17 @@
       <c r="K25" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_15</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2">
         <v>15</v>
@@ -1602,14 +2301,17 @@
       <c r="K26" s="2">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2">
         <v>16</v>
@@ -1639,14 +2341,17 @@
       <c r="K27" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C28" s="2">
         <v>9</v>
@@ -1670,14 +2375,17 @@
       <c r="K28" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_10</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C29" s="2">
         <v>10</v>
@@ -1686,7 +2394,7 @@
         <v>270</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -1700,14 +2408,17 @@
       <c r="K29" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_elite_11</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C30" s="2">
         <v>11</v>
@@ -1731,14 +2442,17 @@
       <c r="K30" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_17</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C31" s="2">
         <v>17</v>
@@ -1768,14 +2482,17 @@
       <c r="K31" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>evt_zako_18</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2">
         <v>18</v>
@@ -1805,27 +2522,30 @@
       <c r="K32" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D33" s="2">
         <v>360</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>